--- a/kits/cra-readiness/samples/mossbyte-sprout-s1/deliverables/sbom/sprout-s1-2.3.0-components.xlsx
+++ b/kits/cra-readiness/samples/mossbyte-sprout-s1/deliverables/sbom/sprout-s1-2.3.0-components.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>55f9747c1095e75a26193b5143f5475fadeeb951a6d02ef95ac9fa5532f7cf8c</t>
+          <t>4f5ab08eeaf59d6b6bf892c7c7d87284c258d0f53277fc0e528fac63fc85e3c2</t>
         </is>
       </c>
     </row>

--- a/kits/cra-readiness/samples/mossbyte-sprout-s1/deliverables/sbom/sprout-s1-2.3.0-components.xlsx
+++ b/kits/cra-readiness/samples/mossbyte-sprout-s1/deliverables/sbom/sprout-s1-2.3.0-components.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>4f5ab08eeaf59d6b6bf892c7c7d87284c258d0f53277fc0e528fac63fc85e3c2</t>
+          <t>bd8a853f91a04f9e508902a870f70683058e7fd9fa4c8ba0b6fcec0acaf0956e</t>
         </is>
       </c>
     </row>
